--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J61-HealthcareFacilityTypeCode-DMP.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J61-HealthcareFacilityTypeCode-DMP.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,7 +490,7 @@
     <t>SA63</t>
   </si>
   <si>
-    <t>Communauté Professionnelle Territoriale de Santé</t>
+    <t>Structures de coordination et d'orientation</t>
   </si>
   <si>
     <t>SA64</t>
